--- a/tools/importer/reports/import-download-detail.report.xlsx
+++ b/tools/importer/reports/import-download-detail.report.xlsx
@@ -361,7 +361,7 @@
     <t>try/download/search-in-community</t>
   </si>
   <si>
-    <t>2026-07-07T22:20:33.993Z</t>
+    <t>2026-07-20T21:17:32.296Z</t>
   </si>
   <si>
     <t>MongoDB</t>
